--- a/jogos_2024-12-06.xlsx
+++ b/jogos_2024-12-06.xlsx
@@ -643,22 +643,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>PSIS Semarang</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -669,65 +669,65 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="M2" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="N2" t="n">
-        <v>4.3</v>
+        <v>6.75</v>
       </c>
       <c r="O2" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="P2" t="n">
         <v>2.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.75</v>
+        <v>6.5</v>
       </c>
       <c r="R2" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S2" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="T2" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="U2" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W2" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="X2" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AA2" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.77</v>
+        <v>2.05</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>['15']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -736,16 +736,16 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.15</v>
+        <v>2.7</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2.88</v>
+        <v>3.75</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45632.22916666666</v>
@@ -772,22 +772,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PSIS Semarang</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -798,83 +798,83 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="M3" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="N3" t="n">
-        <v>6.75</v>
+        <v>4.3</v>
       </c>
       <c r="O3" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="P3" t="n">
         <v>2.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.5</v>
+        <v>4.75</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="S3" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="T3" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="X3" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.05</v>
+        <v>1.77</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
+          <t>['15']</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG3" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.7</v>
+        <v>2.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AJ3" t="n">
-        <v>3.75</v>
+        <v>2.88</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45632.22916666666</v>
@@ -1159,109 +1159,109 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
         <v>2</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N6" t="n">
         <v>3</v>
       </c>
-      <c r="I6" t="n">
+      <c r="O6" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P6" t="n">
         <v>2</v>
       </c>
-      <c r="J6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
+      <c r="Q6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AC6" t="n">
         <v>1.83</v>
       </c>
-      <c r="M6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W6" t="n">
+      <c r="AD6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>['55', '70']</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
         <v>1.27</v>
       </c>
-      <c r="X6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>['3', '11']</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>['13', '29', '48']</t>
-        </is>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AH6" t="n">
-        <v>1.76</v>
+        <v>1.54</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45632.41666666666</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1303,10 +1303,10 @@
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>7</v>
+        <v>2.8</v>
       </c>
       <c r="M7" t="n">
-        <v>4.33</v>
+        <v>3.1</v>
       </c>
       <c r="N7" t="n">
-        <v>1.33</v>
+        <v>2.25</v>
       </c>
       <c r="O7" t="n">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="P7" t="n">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.83</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="S7" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="T7" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="U7" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="V7" t="n">
         <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="X7" t="n">
-        <v>3.85</v>
+        <v>3.25</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AC7" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>['54']</t>
+          <t>['1']</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>['24']</t>
+          <t>['58']</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>3.1</v>
+        <v>1.47</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.03</v>
+        <v>1.33</v>
       </c>
       <c r="AI7" t="n">
-        <v>4.33</v>
+        <v>2.25</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45632.41666666666</v>
@@ -1417,109 +1417,109 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hapoel Umm al-Fahm</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>7</v>
+      </c>
+      <c r="M8" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="O8" t="n">
+        <v>7</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X8" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC8" t="n">
         <v>2</v>
       </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="M8" t="n">
-        <v>4</v>
-      </c>
-      <c r="N8" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>6</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AD8" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['14', '57']</t>
+          <t>['54']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['24']</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.08</v>
+        <v>3.1</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.49</v>
+        <v>1.03</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.3</v>
+        <v>4.33</v>
       </c>
       <c r="AJ8" t="n">
-        <v>3.6</v>
+        <v>1.25</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45632.41666666666</v>
@@ -1546,25 +1546,25 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" t="n">
         <v>2</v>
       </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1572,83 +1572,83 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="M9" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="O9" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="R9" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="T9" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="U9" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W9" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="X9" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['3', '11']</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>['55', '70']</t>
+          <t>['13', '29', '48']</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.54</v>
+        <v>1.76</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45632.41666666666</v>
@@ -1675,19 +1675,19 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Umm al-Fahm</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
@@ -1701,55 +1701,55 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.8</v>
+        <v>1.42</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="N10" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>6</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T10" t="n">
         <v>2.25</v>
       </c>
-      <c r="O10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.75</v>
-      </c>
       <c r="U10" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W10" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="X10" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.25</v>
+        <v>2.3</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AC10" t="n">
         <v>1.8</v>
@@ -1759,25 +1759,25 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['1']</t>
+          <t>['14', '57']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>['58']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.47</v>
+        <v>1.08</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.33</v>
+        <v>2.49</v>
       </c>
       <c r="AI10" t="n">
-        <v>2.25</v>
+        <v>1.3</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45632.41666666666</v>
@@ -2449,109 +2449,109 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G16" t="n">
         <v>3</v>
       </c>
       <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z16" t="n">
         <v>2</v>
       </c>
-      <c r="I16" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L16" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="M16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O16" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>5</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z16" t="n">
+      <c r="AA16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC16" t="n">
         <v>1.67</v>
       </c>
-      <c r="AA16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2</v>
-      </c>
       <c r="AD16" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['34', '55', '71']</t>
+          <t>['64', '66', '70']</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>['8', '54']</t>
+          <t>['37']</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AJ16" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45632.58333333334</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,22 +2578,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.45</v>
+        <v>1.73</v>
       </c>
       <c r="M17" t="n">
         <v>3.4</v>
       </c>
       <c r="N17" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="O17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>5</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>['34', '55', '71']</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>['8', '54']</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ17" t="n">
         <v>3</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X17" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>['49']</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>['21']</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>2.1</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45632.58333333334</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,22 +2707,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G18" t="n">
         <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.29</v>
+        <v>2.08</v>
       </c>
       <c r="M18" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="N18" t="n">
-        <v>8.5</v>
+        <v>3.27</v>
       </c>
       <c r="O18" t="n">
-        <v>1.67</v>
+        <v>2.65</v>
       </c>
       <c r="P18" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>7.5</v>
+        <v>3.83</v>
       </c>
       <c r="R18" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="S18" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="T18" t="n">
-        <v>2.29</v>
+        <v>2.54</v>
       </c>
       <c r="U18" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="V18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W18" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="X18" t="n">
-        <v>4.75</v>
+        <v>4.22</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.38</v>
+        <v>2.12</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.5</v>
+        <v>2.74</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AC18" t="n">
-        <v>2</v>
+        <v>1.58</v>
       </c>
       <c r="AD18" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>['79', '81']</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>['38', '90+1']</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI18" t="n">
         <v>1.73</v>
       </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>['32', '57']</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>['45']</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AJ18" t="n">
-        <v>4.5</v>
+        <v>2.24</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45632.58333333334</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,25 +2836,25 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Stal Stalowa Wola</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.38</v>
+        <v>4.1</v>
       </c>
       <c r="M19" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="N19" t="n">
-        <v>2.88</v>
+        <v>1.73</v>
       </c>
       <c r="O19" t="n">
-        <v>3</v>
+        <v>4.75</v>
       </c>
       <c r="P19" t="n">
         <v>2.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.25</v>
+        <v>2.38</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S19" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="T19" t="n">
-        <v>2.34</v>
+        <v>2.62</v>
       </c>
       <c r="U19" t="n">
-        <v>1.54</v>
+        <v>1.42</v>
       </c>
       <c r="V19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W19" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="X19" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="Z19" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AD19" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>['58', '86']</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
         <v>2.1</v>
       </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>['64', '66', '70']</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>['37']</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
+      <c r="AH19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AJ19" t="n">
         <v>1.5</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>2.2</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45632.58333333334</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,25 +2965,25 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Voitsberg</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2991,55 +2991,55 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.33</v>
+        <v>2.4</v>
       </c>
       <c r="M20" t="n">
-        <v>5.5</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>6.5</v>
+        <v>2.75</v>
       </c>
       <c r="O20" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="P20" t="n">
-        <v>2.63</v>
+        <v>2.05</v>
       </c>
       <c r="Q20" t="n">
-        <v>7</v>
+        <v>3.4</v>
       </c>
       <c r="R20" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S20" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T20" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="U20" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="V20" t="n">
         <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X20" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AC20" t="n">
         <v>1.8</v>
@@ -3049,25 +3049,25 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>['23']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>['56']</t>
+          <t>['32', '41', '89']</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.02</v>
+        <v>1.33</v>
       </c>
       <c r="AH20" t="n">
-        <v>3.72</v>
+        <v>1.78</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.25</v>
+        <v>1.83</v>
       </c>
       <c r="AJ20" t="n">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45632.58333333334</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,16 +3094,16 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
         <v>1</v>
@@ -3112,7 +3112,7 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.97</v>
+        <v>2.45</v>
       </c>
       <c r="M21" t="n">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>2.24</v>
+        <v>2.8</v>
       </c>
       <c r="O21" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P21" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.65</v>
+        <v>3.25</v>
       </c>
       <c r="R21" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="S21" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="T21" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X21" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>['49']</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>['21']</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ21" t="n">
         <v>2.1</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X21" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>['55', '90+1']</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>['57']</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.83</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45632.58333333334</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,109 +3223,109 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G22" t="n">
         <v>2</v>
       </c>
       <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M22" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N22" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X22" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC22" t="n">
         <v>2</v>
       </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L22" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="M22" t="n">
+      <c r="AD22" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>['32', '57']</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>['45']</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AH22" t="n">
         <v>3.6</v>
       </c>
-      <c r="N22" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="O22" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X22" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>['79', '81']</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>['38', '90+1']</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AI22" t="n">
-        <v>1.73</v>
+        <v>1.2</v>
       </c>
       <c r="AJ22" t="n">
-        <v>2.24</v>
+        <v>4.5</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45632.58333333334</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,25 +3352,25 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Voitsberg</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3378,55 +3378,55 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.4</v>
+        <v>1.33</v>
       </c>
       <c r="M23" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N23" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>7</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S23" t="n">
         <v>3.3</v>
       </c>
-      <c r="N23" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="O23" t="n">
-        <v>3</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.25</v>
-      </c>
       <c r="T23" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="U23" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="V23" t="n">
         <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X23" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="Y23" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AC23" t="n">
         <v>1.8</v>
@@ -3436,25 +3436,25 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['23']</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>['32', '41', '89']</t>
+          <t>['56']</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.33</v>
+        <v>1.02</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.78</v>
+        <v>3.72</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.83</v>
+        <v>1.25</v>
       </c>
       <c r="AJ23" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45632.58333333334</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,19 +3481,19 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Stal Stalowa Wola</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4.1</v>
+        <v>2.97</v>
       </c>
       <c r="M24" t="n">
-        <v>3.6</v>
+        <v>3.54</v>
       </c>
       <c r="N24" t="n">
-        <v>1.73</v>
+        <v>2.24</v>
       </c>
       <c r="O24" t="n">
-        <v>4.75</v>
+        <v>3.2</v>
       </c>
       <c r="P24" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.38</v>
+        <v>2.65</v>
       </c>
       <c r="R24" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="S24" t="n">
-        <v>2.9</v>
+        <v>3.55</v>
       </c>
       <c r="T24" t="n">
-        <v>2.62</v>
+        <v>2.1</v>
       </c>
       <c r="U24" t="n">
-        <v>1.42</v>
+        <v>1.65</v>
       </c>
       <c r="V24" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="X24" t="n">
-        <v>3.8</v>
+        <v>5.25</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.85</v>
+        <v>1.45</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.95</v>
+        <v>2.7</v>
       </c>
       <c r="AA24" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="AC24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>['55', '90+1']</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>['57']</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ24" t="n">
         <v>1.83</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>['58', '86']</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.5</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45632.58333333334</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,22 +3868,22 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SuperSport United</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H27" t="n">
         <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3894,83 +3894,83 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.25</v>
+        <v>1.2</v>
       </c>
       <c r="M27" t="n">
-        <v>2.76</v>
+        <v>7.2</v>
       </c>
       <c r="N27" t="n">
-        <v>2.46</v>
+        <v>12</v>
       </c>
       <c r="O27" t="n">
-        <v>3.95</v>
+        <v>1.53</v>
       </c>
       <c r="P27" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S27" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U27" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q27" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="T27" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.22</v>
-      </c>
       <c r="V27" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="X27" t="n">
-        <v>2.37</v>
+        <v>7</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.75</v>
+        <v>1.36</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>5.25</v>
+        <v>2.12</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.15</v>
+        <v>1.73</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['40', '53', '66']</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>['89']</t>
+          <t>['81']</t>
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.53</v>
+        <v>1.04</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.33</v>
+        <v>5</v>
       </c>
       <c r="AI27" t="n">
-        <v>2.38</v>
+        <v>1.17</v>
       </c>
       <c r="AJ27" t="n">
-        <v>2</v>
+        <v>4.75</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45632.60416666666</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,22 +3997,22 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>SuperSport United</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
         <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.2</v>
+        <v>3.25</v>
       </c>
       <c r="M28" t="n">
-        <v>7.2</v>
+        <v>2.76</v>
       </c>
       <c r="N28" t="n">
-        <v>12</v>
+        <v>2.46</v>
       </c>
       <c r="O28" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X28" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>['89']</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
         <v>1.53</v>
       </c>
-      <c r="P28" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S28" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="T28" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X28" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>['40', '53', '66']</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>['81']</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AH28" t="n">
-        <v>5</v>
+        <v>1.33</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.17</v>
+        <v>2.38</v>
       </c>
       <c r="AJ28" t="n">
-        <v>4.75</v>
+        <v>2</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45632.60416666666</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,25 +4126,25 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="M29" t="n">
-        <v>3.44</v>
+        <v>3.1</v>
       </c>
       <c r="N29" t="n">
-        <v>2.41</v>
+        <v>2.75</v>
       </c>
       <c r="O29" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X29" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD29" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q29" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X29" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>['23']</t>
+          <t>['74', '90+4']</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>['37']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AI29" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45632.625</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,109 +4384,109 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M31" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="O31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X31" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>['23']</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>['37']</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI31" t="n">
         <v>2</v>
       </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M31" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N31" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="O31" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P31" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="X31" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>['74', '90+4']</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AJ31" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45632.625</v>
@@ -4513,109 +4513,109 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
         <v>3</v>
-      </c>
-      <c r="I32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J32" t="n">
-        <v>2</v>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L32" t="n">
-        <v>1.95</v>
       </c>
       <c r="M32" t="n">
         <v>3.2</v>
       </c>
       <c r="N32" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="O32" t="n">
-        <v>2.75</v>
+        <v>3.6</v>
       </c>
       <c r="P32" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="R32" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="S32" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="T32" t="n">
-        <v>3.54</v>
+        <v>3.14</v>
       </c>
       <c r="U32" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="V32" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="W32" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="X32" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AA32" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>['27', '72']</t>
+          <t>['57']</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>['3', '18', '73']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.61</v>
+        <v>1.3</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.67</v>
+        <v>2.4</v>
       </c>
       <c r="AJ32" t="n">
-        <v>2.88</v>
+        <v>1.8</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45632.64583333334</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,25 +4642,25 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -4668,83 +4668,83 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="M33" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="N33" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="O33" t="n">
         <v>3.6</v>
       </c>
       <c r="P33" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="Q33" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="R33" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="S33" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T33" t="n">
         <v>2.5</v>
       </c>
-      <c r="T33" t="n">
-        <v>3.14</v>
-      </c>
       <c r="U33" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="V33" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="W33" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="X33" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.65</v>
+        <v>2.38</v>
       </c>
       <c r="AA33" t="n">
-        <v>4</v>
+        <v>2.38</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.2</v>
+        <v>1.55</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>['57']</t>
+          <t>['18', '39']</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+3']</t>
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AH33" t="n">
         <v>1.3</v>
       </c>
       <c r="AI33" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45632.64583333334</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,109 +4771,109 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G34" t="n">
         <v>2</v>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" t="n">
         <v>2</v>
       </c>
-      <c r="J34" t="n">
-        <v>1</v>
-      </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.5</v>
+        <v>1.95</v>
       </c>
       <c r="M34" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="N34" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O34" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P34" t="n">
         <v>1.95</v>
       </c>
-      <c r="O34" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P34" t="n">
-        <v>2.38</v>
-      </c>
       <c r="Q34" t="n">
-        <v>2.5</v>
+        <v>4.33</v>
       </c>
       <c r="R34" t="n">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="S34" t="n">
-        <v>3.25</v>
+        <v>2.32</v>
       </c>
       <c r="T34" t="n">
-        <v>2.5</v>
+        <v>3.54</v>
       </c>
       <c r="U34" t="n">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="V34" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="W34" t="n">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="X34" t="n">
-        <v>4.4</v>
+        <v>2.75</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.53</v>
+        <v>2.35</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.38</v>
+        <v>1.57</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.38</v>
+        <v>4.5</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.55</v>
+        <v>1.17</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>['18', '39']</t>
+          <t>['27', '72']</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>['45+3']</t>
+          <t>['3', '18', '73']</t>
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.3</v>
+        <v>1.61</v>
       </c>
       <c r="AI34" t="n">
-        <v>2.38</v>
+        <v>1.67</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.57</v>
+        <v>2.88</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45632.64583333334</v>
@@ -4900,25 +4900,25 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.9</v>
+        <v>1.6</v>
       </c>
       <c r="M35" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N35" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="O35" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>5</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X35" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>['51', '73']</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>['25', '66']</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AJ35" t="n">
         <v>3.4</v>
-      </c>
-      <c r="N35" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="O35" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T35" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X35" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>['4', '30', '33', '59']</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>1.57</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45632.64583333334</v>
@@ -5029,22 +5029,22 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G36" t="n">
         <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -5055,55 +5055,55 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="M36" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N36" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O36" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X36" t="n">
         <v>3</v>
       </c>
-      <c r="N36" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O36" t="n">
-        <v>3</v>
-      </c>
-      <c r="P36" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="S36" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="T36" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X36" t="n">
-        <v>2.88</v>
-      </c>
       <c r="Y36" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AA36" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AC36" t="n">
         <v>2</v>
@@ -5113,25 +5113,25 @@
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>['67', '76']</t>
+          <t>['7', '90+3']</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['57']</t>
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.59</v>
+        <v>1.69</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AJ36" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45632.64583333334</v>
@@ -5158,22 +5158,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
         <v>1</v>
@@ -5184,28 +5184,28 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="M37" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="N37" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="O37" t="n">
         <v>2.2</v>
       </c>
       <c r="P37" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R37" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="S37" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="T37" t="n">
         <v>3.1</v>
@@ -5217,50 +5217,50 @@
         <v>1.05</v>
       </c>
       <c r="W37" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="X37" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="Y37" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AA37" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AC37" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>['51', '73']</t>
+          <t>['45+1', '90', '90+1']</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>['25', '66']</t>
+          <t>['3']</t>
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="AI37" t="n">
         <v>1.4</v>
       </c>
       <c r="AJ37" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45632.64583333334</v>
@@ -5416,109 +5416,109 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G39" t="n">
+        <v>2</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="M39" t="n">
         <v>3</v>
       </c>
-      <c r="H39" t="n">
-        <v>1</v>
-      </c>
-      <c r="I39" t="n">
-        <v>1</v>
-      </c>
-      <c r="J39" t="n">
-        <v>1</v>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L39" t="n">
+      <c r="N39" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O39" t="n">
+        <v>3</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X39" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z39" t="n">
         <v>1.57</v>
       </c>
-      <c r="M39" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N39" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="O39" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="P39" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>6</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S39" t="n">
+      <c r="AA39" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>['67', '76']</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ39" t="n">
         <v>2.5</v>
-      </c>
-      <c r="T39" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X39" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>['45+1', '90', '90+1']</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>['3']</t>
-        </is>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>3.75</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45632.64583333334</v>
@@ -5545,22 +5545,22 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -5571,83 +5571,83 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.9</v>
+        <v>3.9</v>
       </c>
       <c r="M40" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N40" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="O40" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="P40" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S40" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X40" t="n">
         <v>3.3</v>
       </c>
-      <c r="N40" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O40" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="P40" t="n">
+      <c r="Y40" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q40" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S40" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T40" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X40" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>2.2</v>
-      </c>
       <c r="Z40" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AA40" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="AB40" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>['4', '30', '33', '59']</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AH40" t="n">
         <v>1.2</v>
       </c>
-      <c r="AC40" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>['7', '90+3']</t>
-        </is>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>['57']</t>
-        </is>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>1.69</v>
-      </c>
       <c r="AI40" t="n">
-        <v>1.62</v>
+        <v>2.75</v>
       </c>
       <c r="AJ40" t="n">
-        <v>2.75</v>
+        <v>1.57</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45632.64583333334</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,23 +5674,23 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G41" t="n">
+        <v>6</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" t="n">
         <v>3</v>
       </c>
-      <c r="H41" t="n">
-        <v>3</v>
-      </c>
-      <c r="I41" t="n">
-        <v>1</v>
-      </c>
       <c r="J41" t="n">
         <v>1</v>
       </c>
@@ -5700,83 +5700,83 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.9</v>
+        <v>1.43</v>
       </c>
       <c r="M41" t="n">
-        <v>3</v>
+        <v>4.94</v>
       </c>
       <c r="N41" t="n">
-        <v>3.9</v>
+        <v>6.6</v>
       </c>
       <c r="O41" t="n">
-        <v>2.75</v>
+        <v>1.91</v>
       </c>
       <c r="P41" t="n">
-        <v>1.95</v>
+        <v>2.63</v>
       </c>
       <c r="Q41" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="R41" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="S41" t="n">
-        <v>2.38</v>
+        <v>4</v>
       </c>
       <c r="T41" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="U41" t="n">
-        <v>1.29</v>
+        <v>1.67</v>
       </c>
       <c r="V41" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W41" t="n">
-        <v>1.43</v>
+        <v>1.14</v>
       </c>
       <c r="X41" t="n">
-        <v>2.7</v>
+        <v>5.31</v>
       </c>
       <c r="Y41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z41" t="n">
         <v>2.4</v>
       </c>
-      <c r="Z41" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AA41" t="n">
-        <v>4.3</v>
+        <v>2.23</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.19</v>
+        <v>1.65</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.62</v>
+        <v>2.25</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>['45+1', '50', '76']</t>
+          <t>['20', '34', '45+2', '54', '63', '85']</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>['32', '79', '89']</t>
+          <t>['10']</t>
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.68</v>
+        <v>2.8</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="AJ41" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45632.66666666666</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,22 +5803,22 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -5829,83 +5829,83 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="M42" t="n">
-        <v>3.5</v>
+        <v>3.61</v>
       </c>
       <c r="N42" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="O42" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="P42" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="R42" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="S42" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="T42" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="U42" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="V42" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W42" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="X42" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="AC42" t="n">
         <v>1.5</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['19', '48']</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['63']</t>
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="AJ42" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45632.66666666666</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,22 +5932,22 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -5958,83 +5958,83 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="M43" t="n">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="N43" t="n">
-        <v>3.37</v>
+        <v>3.13</v>
       </c>
       <c r="O43" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="P43" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q43" t="n">
         <v>3.6</v>
       </c>
       <c r="R43" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="S43" t="n">
-        <v>2.63</v>
+        <v>3.1</v>
       </c>
       <c r="T43" t="n">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="U43" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="V43" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W43" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="X43" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="Y43" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z43" t="n">
         <v>2.15</v>
       </c>
-      <c r="Z43" t="n">
+      <c r="AA43" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>['47', '56', '59']</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG43" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH43" t="n">
         <v>1.67</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE43" t="inlineStr">
-        <is>
-          <t>['12']</t>
-        </is>
-      </c>
-      <c r="AF43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG43" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>1.62</v>
       </c>
       <c r="AI43" t="n">
         <v>1.8</v>
       </c>
       <c r="AJ43" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45632.66666666666</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>KMSK Deinze</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6083,87 +6083,87 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.38</v>
+        <v>10</v>
       </c>
       <c r="M44" t="n">
-        <v>3.4</v>
+        <v>5.25</v>
       </c>
       <c r="N44" t="n">
-        <v>2.55</v>
+        <v>1.22</v>
       </c>
       <c r="O44" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="P44" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S44" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X44" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD44" t="n">
         <v>2</v>
       </c>
-      <c r="Q44" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R44" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S44" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T44" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V44" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X44" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y44" t="n">
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG44" t="n">
         <v>2.05</v>
       </c>
-      <c r="Z44" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB44" t="n">
+      <c r="AH44" t="n">
         <v>1.22</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG44" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>1.42</v>
       </c>
       <c r="AI44" t="n">
         <v>2.2</v>
       </c>
       <c r="AJ44" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AK44" s="3" t="n">
         <v>45632.66666666666</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,109 +6190,109 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="M45" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N45" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="O45" t="n">
         <v>3</v>
       </c>
-      <c r="H45" t="n">
-        <v>2</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" t="n">
-        <v>1</v>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L45" t="n">
+      <c r="P45" t="n">
         <v>2.1</v>
       </c>
-      <c r="M45" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N45" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O45" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="P45" t="n">
-        <v>2.3</v>
-      </c>
       <c r="Q45" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R45" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S45" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X45" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB45" t="n">
         <v>1.25</v>
       </c>
-      <c r="S45" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T45" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U45" t="n">
+      <c r="AC45" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>['12']</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG45" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH45" t="n">
         <v>1.62</v>
       </c>
-      <c r="V45" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X45" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AA45" t="n">
+      <c r="AI45" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ45" t="n">
         <v>2.25</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AE45" t="inlineStr">
-        <is>
-          <t>['55', '60', '74']</t>
-        </is>
-      </c>
-      <c r="AF45" t="inlineStr">
-        <is>
-          <t>['45', '90+3']</t>
-        </is>
-      </c>
-      <c r="AG45" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>2.15</v>
       </c>
       <c r="AK45" s="3" t="n">
         <v>45632.66666666666</v>
@@ -6319,16 +6319,16 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H46" t="n">
         <v>2</v>
@@ -6345,83 +6345,83 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="M46" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="N46" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="O46" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="P46" t="n">
         <v>2.3</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="R46" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="S46" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="T46" t="n">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="U46" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="V46" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W46" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X46" t="n">
-        <v>4.3</v>
+        <v>5.25</v>
       </c>
       <c r="Y46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>['55', '60', '74']</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>['45', '90+3']</t>
+        </is>
+      </c>
+      <c r="AG46" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH46" t="n">
         <v>1.7</v>
       </c>
-      <c r="Z46" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE46" t="inlineStr">
-        <is>
-          <t>['57', '81']</t>
-        </is>
-      </c>
-      <c r="AF46" t="inlineStr">
-        <is>
-          <t>['31', '88']</t>
-        </is>
-      </c>
-      <c r="AG46" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AI46" t="n">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="AJ46" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AK46" s="3" t="n">
         <v>45632.66666666666</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,25 +6448,25 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -6474,83 +6474,83 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="M47" t="n">
-        <v>3.56</v>
+        <v>3.4</v>
       </c>
       <c r="N47" t="n">
-        <v>3.13</v>
+        <v>3.75</v>
       </c>
       <c r="O47" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="P47" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="R47" t="n">
         <v>1.33</v>
       </c>
       <c r="S47" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="T47" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X47" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>['57', '81']</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>['31', '88']</t>
+        </is>
+      </c>
+      <c r="AG47" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ47" t="n">
         <v>2.4</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V47" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W47" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X47" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AE47" t="inlineStr">
-        <is>
-          <t>['47', '56', '59']</t>
-        </is>
-      </c>
-      <c r="AF47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG47" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>2.2</v>
       </c>
       <c r="AK47" s="3" t="n">
         <v>45632.66666666666</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,25 +6577,25 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I48" t="n">
         <v>1</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -6603,43 +6603,43 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.17</v>
+        <v>1.9</v>
       </c>
       <c r="M48" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="N48" t="n">
-        <v>2.96</v>
+        <v>3.9</v>
       </c>
       <c r="O48" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="P48" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="R48" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="S48" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="T48" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U48" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V48" t="n">
         <v>1.06</v>
       </c>
       <c r="W48" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="X48" t="n">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="Y48" t="n">
         <v>2.4</v>
@@ -6648,38 +6648,38 @@
         <v>1.53</v>
       </c>
       <c r="AA48" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>['10', '90+7']</t>
+          <t>['45+1', '50', '76']</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['32', '79', '89']</t>
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.38</v>
+        <v>1.19</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AI48" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AJ48" t="n">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="AK48" s="3" t="n">
         <v>45632.66666666666</v>
@@ -6706,16 +6706,16 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -6732,65 +6732,65 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.93</v>
+        <v>2.38</v>
       </c>
       <c r="M49" t="n">
         <v>3.4</v>
       </c>
       <c r="N49" t="n">
-        <v>3.55</v>
+        <v>2.55</v>
       </c>
       <c r="O49" t="n">
-        <v>2.88</v>
+        <v>3.6</v>
       </c>
       <c r="P49" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="R49" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="S49" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="T49" t="n">
-        <v>2.63</v>
+        <v>3.4</v>
       </c>
       <c r="U49" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="V49" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W49" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="X49" t="n">
-        <v>3.75</v>
+        <v>2.9</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="Z49" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AA49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AD49" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>['88']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
@@ -6799,16 +6799,16 @@
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.66</v>
+        <v>1.42</v>
       </c>
       <c r="AI49" t="n">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="AJ49" t="n">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="AK49" s="3" t="n">
         <v>45632.66666666666</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,65 +6861,65 @@
         </is>
       </c>
       <c r="L50" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="M50" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N50" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="O50" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P50" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S50" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W50" t="n">
         <v>1.36</v>
       </c>
-      <c r="M50" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="N50" t="n">
-        <v>7</v>
-      </c>
-      <c r="O50" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="P50" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R50" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S50" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T50" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U50" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V50" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W50" t="n">
-        <v>1.07</v>
-      </c>
       <c r="X50" t="n">
-        <v>5.55</v>
+        <v>2.95</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.44</v>
+        <v>2.4</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.7</v>
+        <v>1.53</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.95</v>
+        <v>4</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.84</v>
+        <v>1.22</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AD50" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>['24', '66']</t>
+          <t>['10', '90+7']</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
@@ -6928,16 +6928,16 @@
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>1.08</v>
+        <v>1.38</v>
       </c>
       <c r="AH50" t="n">
-        <v>3.25</v>
+        <v>1.55</v>
       </c>
       <c r="AI50" t="n">
-        <v>1.29</v>
+        <v>1.8</v>
       </c>
       <c r="AJ50" t="n">
-        <v>3.6</v>
+        <v>2.25</v>
       </c>
       <c r="AK50" s="3" t="n">
         <v>45632.66666666666</v>
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,83 +6990,83 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="M51" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N51" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="O51" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="P51" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="Q51" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="R51" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="S51" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="T51" t="n">
         <v>2.4</v>
       </c>
       <c r="U51" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="V51" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W51" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X51" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Z51" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG51" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ51" t="n">
         <v>2.2</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AE51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG51" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>2.4</v>
       </c>
       <c r="AK51" s="3" t="n">
         <v>45632.66666666666</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,109 +7093,109 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G52" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="M52" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N52" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O52" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P52" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S52" t="n">
+        <v>3</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V52" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W52" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X52" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z52" t="n">
         <v>2</v>
       </c>
-      <c r="H52" t="n">
-        <v>1</v>
-      </c>
-      <c r="I52" t="n">
-        <v>1</v>
-      </c>
-      <c r="J52" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L52" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="M52" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="N52" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="O52" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P52" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R52" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S52" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T52" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="U52" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="V52" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W52" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X52" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z52" t="n">
+      <c r="AA52" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>['88']</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG52" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ52" t="n">
         <v>2.25</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE52" t="inlineStr">
-        <is>
-          <t>['19', '48']</t>
-        </is>
-      </c>
-      <c r="AF52" t="inlineStr">
-        <is>
-          <t>['63']</t>
-        </is>
-      </c>
-      <c r="AG52" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AI52" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AJ52" t="n">
-        <v>2.07</v>
       </c>
       <c r="AK52" s="3" t="n">
         <v>45632.66666666666</v>
@@ -7222,22 +7222,22 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Martigues</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -7248,22 +7248,22 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.45</v>
+        <v>3.37</v>
       </c>
       <c r="M53" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="N53" t="n">
-        <v>5.7</v>
+        <v>1.92</v>
       </c>
       <c r="O53" t="n">
-        <v>2.1</v>
+        <v>5.5</v>
       </c>
       <c r="P53" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q53" t="n">
-        <v>6.5</v>
+        <v>2.2</v>
       </c>
       <c r="R53" t="n">
         <v>1.36</v>
@@ -7281,50 +7281,50 @@
         <v>1.04</v>
       </c>
       <c r="W53" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="X53" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="Y53" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AA53" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AC53" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>['29', '71']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['88']</t>
         </is>
       </c>
       <c r="AG53" t="n">
-        <v>1.07</v>
+        <v>2.25</v>
       </c>
       <c r="AH53" t="n">
-        <v>2.55</v>
+        <v>1.12</v>
       </c>
       <c r="AI53" t="n">
-        <v>1.36</v>
+        <v>3.1</v>
       </c>
       <c r="AJ53" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="AK53" s="3" t="n">
         <v>45632.66666666666</v>
@@ -7351,22 +7351,22 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Martigues</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -7377,22 +7377,22 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>3.37</v>
+        <v>1.45</v>
       </c>
       <c r="M54" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="N54" t="n">
-        <v>1.92</v>
+        <v>5.7</v>
       </c>
       <c r="O54" t="n">
-        <v>5.5</v>
+        <v>2.1</v>
       </c>
       <c r="P54" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.2</v>
+        <v>6.5</v>
       </c>
       <c r="R54" t="n">
         <v>1.36</v>
@@ -7410,50 +7410,50 @@
         <v>1.04</v>
       </c>
       <c r="W54" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="X54" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AA54" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AB54" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>['29', '71']</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG54" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AI54" t="n">
         <v>1.36</v>
       </c>
-      <c r="AC54" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF54" t="inlineStr">
-        <is>
-          <t>['88']</t>
-        </is>
-      </c>
-      <c r="AG54" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH54" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AI54" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AJ54" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="AK54" s="3" t="n">
         <v>45632.66666666666</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>KMSK Deinze</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7502,87 +7502,87 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>10</v>
+        <v>1.95</v>
       </c>
       <c r="M55" t="n">
-        <v>5.25</v>
+        <v>3.75</v>
       </c>
       <c r="N55" t="n">
-        <v>1.22</v>
+        <v>3.6</v>
       </c>
       <c r="O55" t="n">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="P55" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>4</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S55" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T55" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q55" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R55" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S55" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T55" t="n">
-        <v>2.63</v>
-      </c>
       <c r="U55" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="V55" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W55" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X55" t="n">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="Z55" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AA55" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG55" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ55" t="n">
         <v>2.4</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG55" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI55" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>1.73</v>
       </c>
       <c r="AK55" s="3" t="n">
         <v>45632.66666666666</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,25 +7609,25 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -7635,28 +7635,28 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="M56" t="n">
-        <v>4.94</v>
+        <v>5.25</v>
       </c>
       <c r="N56" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="O56" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="P56" t="n">
         <v>2.63</v>
       </c>
       <c r="Q56" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="R56" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S56" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="T56" t="n">
         <v>2.1</v>
@@ -7668,50 +7668,50 @@
         <v>1.01</v>
       </c>
       <c r="W56" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="X56" t="n">
-        <v>5.31</v>
+        <v>5.55</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="Z56" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="AA56" t="n">
-        <v>2.23</v>
+        <v>1.95</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="AC56" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AD56" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AE56" t="inlineStr">
         <is>
-          <t>['20', '34', '45+2', '54', '63', '85']</t>
+          <t>['24', '66']</t>
         </is>
       </c>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>['10']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG56" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AH56" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="AI56" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AJ56" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AK56" s="3" t="n">
         <v>45632.66666666666</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,19 +7867,19 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I58" t="n">
         <v>1</v>
@@ -7893,55 +7893,55 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.35</v>
+        <v>4.5</v>
       </c>
       <c r="M58" t="n">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="N58" t="n">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="O58" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="P58" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.75</v>
+        <v>2.4</v>
       </c>
       <c r="R58" t="n">
-        <v>1.57</v>
+        <v>1.39</v>
       </c>
       <c r="S58" t="n">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="T58" t="n">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="U58" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="V58" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="W58" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="X58" t="n">
-        <v>2.55</v>
+        <v>3.4</v>
       </c>
       <c r="Y58" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AA58" t="n">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AC58" t="n">
         <v>2.1</v>
@@ -7951,25 +7951,25 @@
       </c>
       <c r="AE58" t="inlineStr">
         <is>
-          <t>['20']</t>
+          <t>['38', '78', '80']</t>
         </is>
       </c>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>['30', '66', '74']</t>
+          <t>['19', '51', '63', '66']</t>
         </is>
       </c>
       <c r="AG58" t="n">
-        <v>1.31</v>
+        <v>2.1</v>
       </c>
       <c r="AH58" t="n">
-        <v>1.41</v>
+        <v>1.15</v>
       </c>
       <c r="AI58" t="n">
-        <v>1.83</v>
+        <v>3</v>
       </c>
       <c r="AJ58" t="n">
-        <v>2.38</v>
+        <v>1.53</v>
       </c>
       <c r="AK58" s="3" t="n">
         <v>45632.6875</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,25 +7996,25 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G59" t="n">
         <v>2</v>
       </c>
       <c r="H59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I59" t="n">
         <v>2</v>
       </c>
       <c r="J59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -8022,83 +8022,83 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.7</v>
+        <v>4.33</v>
       </c>
       <c r="M59" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="N59" t="n">
-        <v>2.5</v>
+        <v>1.65</v>
       </c>
       <c r="O59" t="n">
-        <v>3.25</v>
+        <v>4.75</v>
       </c>
       <c r="P59" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q59" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q59" t="n">
-        <v>3.1</v>
-      </c>
       <c r="R59" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="S59" t="n">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="T59" t="n">
-        <v>2.75</v>
+        <v>2.35</v>
       </c>
       <c r="U59" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="V59" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W59" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X59" t="n">
         <v>3.5</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="Z59" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AA59" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AC59" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AD59" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AE59" t="inlineStr">
         <is>
-          <t>['4', '14']</t>
+          <t>['25', '39']</t>
         </is>
       </c>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>['13']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG59" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AH59" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AI59" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="AJ59" t="n">
-        <v>1.83</v>
+        <v>1.44</v>
       </c>
       <c r="AK59" s="3" t="n">
         <v>45632.6875</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,109 +8125,109 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Caldiero Terme</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H60" t="n">
+        <v>1</v>
+      </c>
+      <c r="I60" t="n">
+        <v>1</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M60" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N60" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O60" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P60" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R60" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S60" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V60" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W60" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X60" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC60" t="n">
         <v>2</v>
       </c>
-      <c r="I60" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" t="n">
-        <v>1</v>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L60" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="M60" t="n">
-        <v>4.04</v>
-      </c>
-      <c r="N60" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="O60" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="P60" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>5</v>
-      </c>
-      <c r="R60" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S60" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T60" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U60" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V60" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W60" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X60" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="Y60" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Z60" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA60" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB60" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC60" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AD60" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
-          <t>['51', '59', '69']</t>
+          <t>['21', '65', '79', '83', '87']</t>
         </is>
       </c>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>['37', '48']</t>
+          <t>['45']</t>
         </is>
       </c>
       <c r="AG60" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AH60" t="n">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="AI60" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AJ60" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AK60" s="3" t="n">
         <v>45632.6875</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,25 +8254,25 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -8280,83 +8280,83 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>4.33</v>
+        <v>2.35</v>
       </c>
       <c r="M61" t="n">
-        <v>3.9</v>
+        <v>2.88</v>
       </c>
       <c r="N61" t="n">
-        <v>1.65</v>
+        <v>3</v>
       </c>
       <c r="O61" t="n">
-        <v>4.75</v>
+        <v>3.2</v>
       </c>
       <c r="P61" t="n">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="Q61" t="n">
-        <v>2.2</v>
+        <v>3.75</v>
       </c>
       <c r="R61" t="n">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="S61" t="n">
-        <v>3.2</v>
+        <v>2.25</v>
       </c>
       <c r="T61" t="n">
-        <v>2.35</v>
+        <v>3.75</v>
       </c>
       <c r="U61" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="V61" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="W61" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="X61" t="n">
-        <v>3.5</v>
+        <v>2.55</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="Z61" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AA61" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="AC61" t="n">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="AD61" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="AE61" t="inlineStr">
         <is>
-          <t>['25', '39']</t>
+          <t>['20']</t>
         </is>
       </c>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['30', '66', '74']</t>
         </is>
       </c>
       <c r="AG61" t="n">
-        <v>2.05</v>
+        <v>1.31</v>
       </c>
       <c r="AH61" t="n">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="AI61" t="n">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="AJ61" t="n">
-        <v>1.44</v>
+        <v>2.38</v>
       </c>
       <c r="AK61" s="3" t="n">
         <v>45632.6875</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,19 +8383,19 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I62" t="n">
         <v>1</v>
@@ -8409,83 +8409,83 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="M62" t="n">
         <v>3.6</v>
       </c>
       <c r="N62" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="O62" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="P62" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>6</v>
+      </c>
+      <c r="R62" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S62" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T62" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V62" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W62" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X62" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y62" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q62" t="n">
-        <v>5</v>
-      </c>
-      <c r="R62" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S62" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T62" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U62" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V62" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W62" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X62" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y62" t="n">
-        <v>2.1</v>
-      </c>
       <c r="Z62" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AA62" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AC62" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AD62" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AE62" t="inlineStr">
         <is>
-          <t>['34', '54']</t>
+          <t>['44']</t>
         </is>
       </c>
       <c r="AF62" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['66']</t>
         </is>
       </c>
       <c r="AG62" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AH62" t="n">
-        <v>2.24</v>
+        <v>1.93</v>
       </c>
       <c r="AI62" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AJ62" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="AK62" s="3" t="n">
         <v>45632.6875</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,16 +8512,16 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H63" t="n">
         <v>1</v>
@@ -8530,7 +8530,7 @@
         <v>2</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -8538,83 +8538,83 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.85</v>
+        <v>2.7</v>
       </c>
       <c r="M63" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="N63" t="n">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="O63" t="n">
-        <v>2.63</v>
+        <v>3.25</v>
       </c>
       <c r="P63" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="Q63" t="n">
-        <v>4.75</v>
+        <v>3.1</v>
       </c>
       <c r="R63" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="S63" t="n">
-        <v>2.5</v>
+        <v>2.85</v>
       </c>
       <c r="T63" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="U63" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V63" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W63" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X63" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB63" t="n">
         <v>1.3</v>
       </c>
-      <c r="V63" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W63" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="X63" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y63" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z63" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA63" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB63" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AC63" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="AD63" t="n">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="AE63" t="inlineStr">
         <is>
-          <t>['2', '18', '61']</t>
+          <t>['4', '14']</t>
         </is>
       </c>
       <c r="AF63" t="inlineStr">
         <is>
-          <t>['52']</t>
+          <t>['13']</t>
         </is>
       </c>
       <c r="AG63" t="n">
-        <v>1.18</v>
+        <v>1.75</v>
       </c>
       <c r="AH63" t="n">
-        <v>1.67</v>
+        <v>1.3</v>
       </c>
       <c r="AI63" t="n">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="AJ63" t="n">
-        <v>3</v>
+        <v>1.83</v>
       </c>
       <c r="AK63" s="3" t="n">
         <v>45632.6875</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,25 +8641,25 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G64" t="n">
+        <v>3</v>
+      </c>
+      <c r="H64" t="n">
         <v>2</v>
       </c>
-      <c r="H64" t="n">
-        <v>1</v>
-      </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -8667,83 +8667,83 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.74</v>
+        <v>1.63</v>
       </c>
       <c r="M64" t="n">
-        <v>3.04</v>
+        <v>4.04</v>
       </c>
       <c r="N64" t="n">
-        <v>2.79</v>
+        <v>5.25</v>
       </c>
       <c r="O64" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="P64" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>5</v>
+      </c>
+      <c r="R64" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S64" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V64" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W64" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X64" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD64" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q64" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R64" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S64" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T64" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U64" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V64" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W64" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="X64" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Y64" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="Z64" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA64" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB64" t="n">
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>['51', '59', '69']</t>
+        </is>
+      </c>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>['37', '48']</t>
+        </is>
+      </c>
+      <c r="AG64" t="n">
         <v>1.18</v>
       </c>
-      <c r="AC64" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD64" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE64" t="inlineStr">
-        <is>
-          <t>['87', '90+3']</t>
-        </is>
-      </c>
-      <c r="AF64" t="inlineStr">
-        <is>
-          <t>['56']</t>
-        </is>
-      </c>
-      <c r="AG64" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AH64" t="n">
-        <v>1.47</v>
+        <v>2.15</v>
       </c>
       <c r="AI64" t="n">
-        <v>1.91</v>
+        <v>1.44</v>
       </c>
       <c r="AJ64" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="AK64" s="3" t="n">
         <v>45632.6875</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,19 +8770,19 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G65" t="n">
         <v>2</v>
       </c>
       <c r="H65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I65" t="n">
         <v>1</v>
@@ -8796,83 +8796,83 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.33</v>
+        <v>1.7</v>
       </c>
       <c r="M65" t="n">
-        <v>2.98</v>
+        <v>3.6</v>
       </c>
       <c r="N65" t="n">
-        <v>3.46</v>
+        <v>4.2</v>
       </c>
       <c r="O65" t="n">
-        <v>2.95</v>
+        <v>2.38</v>
       </c>
       <c r="P65" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="Q65" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="R65" t="n">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="S65" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T65" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V65" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W65" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X65" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>['34', '54']</t>
+        </is>
+      </c>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG65" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH65" t="n">
         <v>2.24</v>
       </c>
-      <c r="T65" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="U65" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="V65" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W65" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="X65" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Y65" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Z65" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AA65" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AB65" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AC65" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD65" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE65" t="inlineStr">
-        <is>
-          <t>['8', '79']</t>
-        </is>
-      </c>
-      <c r="AF65" t="inlineStr">
-        <is>
-          <t>['73']</t>
-        </is>
-      </c>
-      <c r="AG65" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH65" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AI65" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="AJ65" t="n">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="AK65" s="3" t="n">
         <v>45632.6875</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,109 +8899,109 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Sestri Levante</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H66" t="n">
+        <v>1</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M66" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N66" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O66" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P66" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>7</v>
+      </c>
+      <c r="R66" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S66" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T66" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V66" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W66" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X66" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>['48', '52', '70', '77']</t>
+        </is>
+      </c>
+      <c r="AF66" t="inlineStr">
+        <is>
+          <t>['64']</t>
+        </is>
+      </c>
+      <c r="AG66" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AH66" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AI66" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AJ66" t="n">
         <v>4</v>
-      </c>
-      <c r="I66" t="n">
-        <v>1</v>
-      </c>
-      <c r="J66" t="n">
-        <v>1</v>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L66" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="M66" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N66" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="O66" t="n">
-        <v>5</v>
-      </c>
-      <c r="P66" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R66" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S66" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T66" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U66" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V66" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W66" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X66" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y66" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z66" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA66" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB66" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC66" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD66" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE66" t="inlineStr">
-        <is>
-          <t>['38', '78', '80']</t>
-        </is>
-      </c>
-      <c r="AF66" t="inlineStr">
-        <is>
-          <t>['19', '51', '63', '66']</t>
-        </is>
-      </c>
-      <c r="AG66" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH66" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AI66" t="n">
-        <v>3</v>
-      </c>
-      <c r="AJ66" t="n">
-        <v>1.53</v>
       </c>
       <c r="AK66" s="3" t="n">
         <v>45632.6875</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,22 +9028,22 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H67" t="n">
         <v>1</v>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -9054,22 +9054,22 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="M67" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="N67" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="O67" t="n">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="P67" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="Q67" t="n">
-        <v>6</v>
+        <v>4.75</v>
       </c>
       <c r="R67" t="n">
         <v>1.5</v>
@@ -9084,53 +9084,53 @@
         <v>1.3</v>
       </c>
       <c r="V67" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="W67" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="X67" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="Y67" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AA67" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AC67" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AD67" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AE67" t="inlineStr">
         <is>
-          <t>['44']</t>
+          <t>['2', '18', '61']</t>
         </is>
       </c>
       <c r="AF67" t="inlineStr">
         <is>
-          <t>['66']</t>
+          <t>['52']</t>
         </is>
       </c>
       <c r="AG67" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AH67" t="n">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="AI67" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AJ67" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="AK67" s="3" t="n">
         <v>45632.6875</v>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,16 +9157,16 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sestri Levante</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H68" t="n">
         <v>1</v>
@@ -9183,22 +9183,22 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.44</v>
+        <v>2.74</v>
       </c>
       <c r="M68" t="n">
-        <v>4.1</v>
+        <v>3.04</v>
       </c>
       <c r="N68" t="n">
-        <v>5.5</v>
+        <v>2.79</v>
       </c>
       <c r="O68" t="n">
-        <v>2.05</v>
+        <v>3.5</v>
       </c>
       <c r="P68" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="Q68" t="n">
-        <v>7</v>
+        <v>3.6</v>
       </c>
       <c r="R68" t="n">
         <v>1.53</v>
@@ -9213,53 +9213,53 @@
         <v>1.25</v>
       </c>
       <c r="V68" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="W68" t="n">
         <v>1.45</v>
       </c>
       <c r="X68" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.1</v>
+        <v>2.34</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AA68" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AB68" t="n">
         <v>1.18</v>
       </c>
       <c r="AC68" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AD68" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AE68" t="inlineStr">
         <is>
-          <t>['48', '52', '70', '77']</t>
+          <t>['87', '90+3']</t>
         </is>
       </c>
       <c r="AF68" t="inlineStr">
         <is>
-          <t>['64']</t>
+          <t>['56']</t>
         </is>
       </c>
       <c r="AG68" t="n">
-        <v>1.11</v>
+        <v>1.45</v>
       </c>
       <c r="AH68" t="n">
-        <v>2.01</v>
+        <v>1.47</v>
       </c>
       <c r="AI68" t="n">
-        <v>1.33</v>
+        <v>1.91</v>
       </c>
       <c r="AJ68" t="n">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="AK68" s="3" t="n">
         <v>45632.6875</v>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,16 +9286,16 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Caldiero Terme</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H69" t="n">
         <v>1</v>
@@ -9304,7 +9304,7 @@
         <v>1</v>
       </c>
       <c r="J69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -9312,83 +9312,83 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.8</v>
+        <v>2.33</v>
       </c>
       <c r="M69" t="n">
-        <v>3.5</v>
+        <v>2.98</v>
       </c>
       <c r="N69" t="n">
-        <v>3.8</v>
+        <v>3.46</v>
       </c>
       <c r="O69" t="n">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="P69" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="Q69" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="R69" t="n">
-        <v>1.44</v>
+        <v>1.59</v>
       </c>
       <c r="S69" t="n">
-        <v>2.63</v>
+        <v>2.24</v>
       </c>
       <c r="T69" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="U69" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="V69" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="W69" t="n">
-        <v>1.39</v>
+        <v>1.54</v>
       </c>
       <c r="X69" t="n">
-        <v>2.85</v>
+        <v>2.48</v>
       </c>
       <c r="Y69" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.7</v>
+        <v>1.42</v>
       </c>
       <c r="AA69" t="n">
-        <v>3.95</v>
+        <v>5.25</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AC69" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AD69" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AE69" t="inlineStr">
         <is>
-          <t>['21', '65', '79', '83', '87']</t>
+          <t>['8', '79']</t>
         </is>
       </c>
       <c r="AF69" t="inlineStr">
         <is>
-          <t>['45']</t>
+          <t>['73']</t>
         </is>
       </c>
       <c r="AG69" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AH69" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AI69" t="n">
-        <v>1.53</v>
+        <v>1.9</v>
       </c>
       <c r="AJ69" t="n">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="AK69" s="3" t="n">
         <v>45632.6875</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,25 +9544,25 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -9570,83 +9570,83 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>5.3</v>
+        <v>2.71</v>
       </c>
       <c r="M71" t="n">
-        <v>5</v>
+        <v>3.15</v>
       </c>
       <c r="N71" t="n">
-        <v>1.5</v>
+        <v>2.71</v>
       </c>
       <c r="O71" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P71" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="Q71" t="n">
-        <v>1.8</v>
+        <v>3.75</v>
       </c>
       <c r="R71" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="S71" t="n">
-        <v>4</v>
+        <v>2.63</v>
       </c>
       <c r="T71" t="n">
-        <v>2</v>
+        <v>3.25</v>
       </c>
       <c r="U71" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V71" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W71" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X71" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>['37']</t>
+        </is>
+      </c>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>['13']</t>
+        </is>
+      </c>
+      <c r="AG71" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI71" t="n">
         <v>1.73</v>
       </c>
-      <c r="V71" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W71" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X71" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Y71" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z71" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA71" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB71" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AC71" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD71" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG71" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AH71" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AI71" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AJ71" t="n">
-        <v>1.29</v>
+        <v>2.3</v>
       </c>
       <c r="AK71" s="3" t="n">
         <v>45632.70833333334</v>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,25 +9802,25 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -9828,83 +9828,83 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.71</v>
+        <v>5.3</v>
       </c>
       <c r="M73" t="n">
-        <v>3.15</v>
+        <v>5</v>
       </c>
       <c r="N73" t="n">
-        <v>2.71</v>
+        <v>1.5</v>
       </c>
       <c r="O73" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P73" t="n">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.75</v>
+        <v>1.8</v>
       </c>
       <c r="R73" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="S73" t="n">
-        <v>2.63</v>
+        <v>4</v>
       </c>
       <c r="T73" t="n">
-        <v>3.25</v>
+        <v>2</v>
       </c>
       <c r="U73" t="n">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="V73" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W73" t="n">
-        <v>1.35</v>
+        <v>1.12</v>
       </c>
       <c r="X73" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z73" t="n">
         <v>3.1</v>
       </c>
-      <c r="Y73" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z73" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AA73" t="n">
-        <v>3.85</v>
+        <v>1.88</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.25</v>
+        <v>1.92</v>
       </c>
       <c r="AC73" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AD73" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AE73" t="inlineStr">
         <is>
-          <t>['37']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF73" t="inlineStr">
         <is>
-          <t>['13']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG73" t="n">
-        <v>1.38</v>
+        <v>3.1</v>
       </c>
       <c r="AH73" t="n">
-        <v>1.6</v>
+        <v>1.08</v>
       </c>
       <c r="AI73" t="n">
-        <v>1.73</v>
+        <v>3.5</v>
       </c>
       <c r="AJ73" t="n">
-        <v>2.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK73" s="3" t="n">
         <v>45632.70833333334</v>
